--- a/docs/3-编队算法设计文档/集中式通信+长机僚机+PID控制+三角队形+1个航段.xlsx
+++ b/docs/3-编队算法设计文档/集中式通信+长机僚机+PID控制+三角队形+1个航段.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2504ef36a9cf56a5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitHub\Simu\simu-cc\docs\3-编队算法设计文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74C6925F-05CE-4EC9-84D4-69732B018041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02539B07-8D00-4F2A-BD39-7DC5319359E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BFCF63F1-0F58-420E-B817-D43F2F82AE0D}"/>
+    <workbookView xWindow="-28920" yWindow="2970" windowWidth="29040" windowHeight="15720" xr2:uid="{BFCF63F1-0F58-420E-B817-D43F2F82AE0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>任务编排</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,19 +148,7 @@
 队形指令</t>
   </si>
   <si>
-    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}
-航段待飞距</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>航段信息{航段号、起始东北高、终点东北高、速度指令}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编队模式{集结、保持、重构}
-上一拍航段信息{航段号、起始东北高、终点东北高、速度指令}
-本体运动状态{东北高+航迹偏航角+速度+航迹倾角}
-上一拍航段待飞距</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -257,21 +245,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}
-航段待飞距</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（僚机其实不需要，为了拉齐这里补充）</t>
-    </r>
+    <t>编队模式{集结、保持、重构}
+上一拍航段信息{航段号、起始东北高、终点东北高、速度指令}
+本体运动状态{东北高+航迹偏航角+速度+航迹倾角}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标指令{东北高+航迹偏航角+航迹倾角+速度}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -570,9 +550,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -594,6 +571,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -603,24 +625,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -630,34 +634,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1007,209 +987,209 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="15"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="11"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="25"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="16"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="2:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>28</v>
+      <c r="D7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>38</v>
+      <c r="F8" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="B13" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">
